--- a/MTD_2025.xlsx
+++ b/MTD_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diego\Documents\Vscode\Projects\MTD_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07847F12-2CE1-4E7A-B584-222067956BCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572FB754-F31A-49F0-8EA3-C5A494F60602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GLOBAL" sheetId="5" r:id="rId1"/>
@@ -21,12 +21,26 @@
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">GLOBAL!$L$6:$L$20</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">GLOBAL!$M$6:$M$20</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">GLOBAL!$M$23</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">GLOBAL!$M$24:$M$28</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">GLOBAL!$N$23</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">GLOBAL!$N$24:$N$28</definedName>
+    <definedName name="_xlchart.v1.14" hidden="1">GLOBAL!$O$23</definedName>
+    <definedName name="_xlchart.v1.15" hidden="1">GLOBAL!$O$24:$O$28</definedName>
+    <definedName name="_xlchart.v1.16" hidden="1">GLOBAL!$M$30</definedName>
+    <definedName name="_xlchart.v1.17" hidden="1">GLOBAL!$M$31:$M$35</definedName>
+    <definedName name="_xlchart.v1.18" hidden="1">GLOBAL!$N$30</definedName>
+    <definedName name="_xlchart.v1.19" hidden="1">GLOBAL!$N$31:$N$35</definedName>
     <definedName name="_xlchart.v1.2" hidden="1">GLOBAL!$N$6:$N$20</definedName>
+    <definedName name="_xlchart.v1.20" hidden="1">GLOBAL!$O$30</definedName>
+    <definedName name="_xlchart.v1.21" hidden="1">GLOBAL!$O$31:$O$35</definedName>
     <definedName name="_xlchart.v1.3" hidden="1">GLOBAL!$O$6:$O$20</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">GLOBAL!$L$6:$L$20</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">GLOBAL!$M$6:$M$20</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">GLOBAL!$N$6:$N$20</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">GLOBAL!$O$6:$O$20</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">GLOBAL!$M$5</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">GLOBAL!$M$6:$M$10</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">GLOBAL!$N$5</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">GLOBAL!$N$6:$N$10</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">GLOBAL!$O$5</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">GLOBAL!$O$6:$O$10</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -49,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="17">
   <si>
     <t>Epochs</t>
   </si>
@@ -106,6 +120,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -520,15 +538,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -584,25 +603,637 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="6" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="6" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="6" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="9" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="22" xfId="6" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="15" xfId="6" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="26" xfId="6" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="6" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="6" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="6" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="7">
     <cellStyle name="20% - Accent1" xfId="1" builtinId="30"/>
     <cellStyle name="40% - Accent1" xfId="4" builtinId="31"/>
     <cellStyle name="60% - Accent1" xfId="2" builtinId="32"/>
     <cellStyle name="Accent1" xfId="3" builtinId="29"/>
+    <cellStyle name="Comma" xfId="6" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="36">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -691,31 +1322,2099 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="101"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="1"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mj-lt"/>
+                <a:ea typeface="+mj-ea"/>
+                <a:cs typeface="+mj-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Accuracy over used energy</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mj-lt"/>
+              <a:ea typeface="+mj-ea"/>
+              <a:cs typeface="+mj-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>MLP</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:ln w="15875">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:tint val="88500"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>GLOBAL!$R$6:$R$10</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>472.3494</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>490.38990000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>496.52519999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>488.34199999999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>506.02140000000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>GLOBAL!$M$6:$M$10</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.95796999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.95104999999999995</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.94906000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.95250000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.96092</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3066-4B4B-8D12-F191A54A6767}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>CNN</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:ln w="15875">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:tint val="55000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>GLOBAL!$S$6:$S$10</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>645.86260000000004</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>646.6404</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>652.29919999999993</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>686.78399999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>662.71040000000005</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>GLOBAL!$N$6:$N$10</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.97799999999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.96951670000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.98361670000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.98463400000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.98465000000000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3066-4B4B-8D12-F191A54A6767}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>ResNet-18</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="triangle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:ln w="15875">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:tint val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>GLOBAL!$T$6:$T$10</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>25808.720300000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>25925.084699999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>26637.750700000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>26279.435400000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25764.280300000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>GLOBAL!$O$6:$O$10</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.98485</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.98023000000000005</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.98751999999999995</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.98323000000000005</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.98951999999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-3066-4B4B-8D12-F191A54A6767}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1124550543"/>
+        <c:axId val="1124534223"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1124550543"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Energy used (J)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+                <a:alpha val="54000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1124534223"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="3500"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1124534223"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Model accuracy</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+                <a:alpha val="54000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1124550543"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:pattFill prst="ltDnDiag">
+          <a:fgClr>
+            <a:schemeClr val="dk1">
+              <a:lumMod val="15000"/>
+              <a:lumOff val="85000"/>
+            </a:schemeClr>
+          </a:fgClr>
+          <a:bgClr>
+            <a:schemeClr val="lt1"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>MLP</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:ln w="15875">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>GLOBAL!$R$24:$R$28</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2597.5892000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2615.6130000000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2629.99</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2695.7507999999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2646.8458000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>GLOBAL!$M$24:$M$28</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.42558000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.4219</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.42796000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.43668000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.42558000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FAE2-4B86-958E-B462C534C2CE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>CNN</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:ln w="15875">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>GLOBAL!$S$24:$S$28</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>3340.0242000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3268.837</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3344.7112000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3249.5574999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3216.8111999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>GLOBAL!$N$24:$N$28</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.59211999999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.59199999999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.59275999999999995</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.59489999999999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.57767999999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-FAE2-4B86-958E-B462C534C2CE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>ResNet-18</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="triangle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:ln w="15875">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>GLOBAL!$T$24:$T$28</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>131587.87600000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>130909.30599999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>129065.30399999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>125967.626</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>125672.97600000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>GLOBAL!$O$24:$O$28</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.69606000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.70364000000000004</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.71728000000000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.71479999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.73358000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-FAE2-4B86-958E-B462C534C2CE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1124550543"/>
+        <c:axId val="1124534223"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1124550543"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Energy used (J)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+                <a:alpha val="54000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1124534223"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1124534223"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="0.75000000000000011"/>
+          <c:min val="0.35000000000000003"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Model accuracy</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+                <a:alpha val="54000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1124550543"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:pattFill prst="ltDnDiag">
+          <a:fgClr>
+            <a:schemeClr val="dk1">
+              <a:lumMod val="15000"/>
+              <a:lumOff val="85000"/>
+            </a:schemeClr>
+          </a:fgClr>
+          <a:bgClr>
+            <a:schemeClr val="lt1"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="101"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="1"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mj-lt"/>
+                <a:ea typeface="+mj-ea"/>
+                <a:cs typeface="+mj-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Accuracy over energy used</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mj-lt"/>
+              <a:ea typeface="+mj-ea"/>
+              <a:cs typeface="+mj-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>MLP</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:ln w="15875">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:tint val="88500"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>GLOBAL!$R$31:$R$35</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>6637.5852999999997</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6661.7039999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6283.0973999999997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6629.2352999999994</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6485.6275000000005</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>GLOBAL!$M$31:$M$35</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.14152000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.14566000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.1484</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.15104000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.15068000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0DDD-4FFF-9FC5-6547D2F31E86}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>CNN</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:ln w="15875">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:tint val="55000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>GLOBAL!$S$31:$S$35</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>7972.7319000000007</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8151.5667999999996</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8386.5390000000007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8281.4526000000005</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8448.9944000000014</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>GLOBAL!$N$31:$N$35</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.21504000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.20785999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.20391999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.2059</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.20172000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0DDD-4FFF-9FC5-6547D2F31E86}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>ResNet-18</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="triangle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:ln w="15875">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:tint val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>GLOBAL!$T$31:$T$35</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>333859.96299999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>326162.473</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>340349.97599999997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>318932.64</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>310033.141</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>GLOBAL!$O$31:$O$35</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.31286000000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.32181999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.3165</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.33235999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.31991999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-0DDD-4FFF-9FC5-6547D2F31E86}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1124550543"/>
+        <c:axId val="1124534223"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1124550543"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="350000"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Energy used (J)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+                <a:alpha val="54000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1124534223"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1124534223"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0.1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Model accuracy</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+                <a:alpha val="54000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1124550543"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:pattFill prst="ltDnDiag">
+          <a:fgClr>
+            <a:schemeClr val="dk1">
+              <a:lumMod val="15000"/>
+              <a:lumOff val="85000"/>
+            </a:schemeClr>
+          </a:fgClr>
+          <a:bgClr>
+            <a:schemeClr val="lt1"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
 <cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.4</cx:f>
+        <cx:f>_xlchart.v1.0</cx:f>
       </cx:strDim>
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.1</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="1">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v1.0</cx:f>
+      </cx:strDim>
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.2</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="2">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v1.0</cx:f>
+      </cx:strDim>
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.3</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{1AB7D9E8-D4E2-4C72-BDC5-A9AD95EE95B0}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f/>
+              <cx:v>MLP</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="1" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{AAAD8E81-5775-481F-B473-FCE4DA44872C}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f/>
+              <cx:v>CNN</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="1"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="1" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{A1F3E258-8243-4130-94C8-F09ED292F634}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f/>
+              <cx:v>RESNET</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="2"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="1" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling max="1" min="0.10000000000000001"/>
+        <cx:title>
+          <cx:tx>
+            <cx:txData>
+              <cx:v>Model accuracy</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:txPr>
+            <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+                </a:rPr>
+                <a:t>Model accuracy</a:t>
+              </a:r>
+            </a:p>
+          </cx:txPr>
+        </cx:title>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+    <cx:legend pos="b" align="ctr" overlay="0"/>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx2.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
       <cx:numDim type="val">
         <cx:f>_xlchart.v1.5</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
-      <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.4</cx:f>
-      </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.6</cx:f>
+        <cx:f>_xlchart.v1.7</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="2">
-      <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.4</cx:f>
-      </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.7</cx:f>
+        <cx:f>_xlchart.v1.9</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -750,52 +3449,255 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="boxWhisker" uniqueId="{1AB7D9E8-D4E2-4C72-BDC5-A9AD95EE95B0}">
+        <cx:series layoutId="boxWhisker" uniqueId="{62E5E8A4-1C1A-4F0E-958B-89A04985F94D}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>_xlchart.v1.4</cx:f>
               <cx:v>MLP</cx:v>
             </cx:txData>
           </cx:tx>
           <cx:dataId val="0"/>
           <cx:layoutPr>
-            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
             <cx:statistics quartileMethod="exclusive"/>
           </cx:layoutPr>
         </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{AAAD8E81-5775-481F-B473-FCE4DA44872C}">
+        <cx:series layoutId="boxWhisker" uniqueId="{25338216-CBD4-4339-AA45-E05E776EBB33}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>_xlchart.v1.6</cx:f>
               <cx:v>CNN</cx:v>
             </cx:txData>
           </cx:tx>
           <cx:dataId val="1"/>
           <cx:layoutPr>
-            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
             <cx:statistics quartileMethod="exclusive"/>
           </cx:layoutPr>
         </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{A1F3E258-8243-4130-94C8-F09ED292F634}">
+        <cx:series layoutId="boxWhisker" uniqueId="{6B781F31-D08F-4641-804E-E68F0685EED5}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>_xlchart.v1.8</cx:f>
               <cx:v>RESNET</cx:v>
             </cx:txData>
           </cx:tx>
           <cx:dataId val="2"/>
           <cx:layoutPr>
-            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
             <cx:statistics quartileMethod="exclusive"/>
           </cx:layoutPr>
         </cx:series>
       </cx:plotAreaRegion>
-      <cx:axis id="0">
+      <cx:axis id="0" hidden="1">
         <cx:catScaling gapWidth="1.5"/>
         <cx:tickLabels/>
       </cx:axis>
       <cx:axis id="1">
-        <cx:valScaling max="1" min="0.10000000000000001"/>
+        <cx:valScaling max="1" min="0.93000000000000005"/>
+        <cx:majorGridlines/>
+        <cx:minorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+    <cx:legend pos="t" align="ctr" overlay="0"/>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx3.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.11</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="1">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.13</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="2">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.15</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>Accuracy by dataset</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="2000" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Display" panose="020F0302020204030204"/>
+            </a:rPr>
+            <a:t>Accuracy by dataset</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{97D44300-416A-4300-8484-B1DD3893D7DD}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.10</cx:f>
+              <cx:v>MLP</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{786BFA6C-9B71-482A-882D-2A12B49800A8}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.12</cx:f>
+              <cx:v>CNN</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="1"/>
+          <cx:layoutPr>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{3F0E56A4-0169-472D-AB4D-700140736DDB}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.14</cx:f>
+              <cx:v>RESNET</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="2"/>
+          <cx:layoutPr>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0" hidden="1">
+        <cx:catScaling gapWidth="1.5"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling max="0.75000000000000011" min="0.35000000000000003"/>
+        <cx:majorGridlines/>
+        <cx:minorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+    <cx:legend pos="t" align="ctr" overlay="0"/>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx4.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.17</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="1">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.19</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="2">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.21</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>Accuracy by dataset</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="2000" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Display" panose="020F0302020204030204"/>
+            </a:rPr>
+            <a:t>Accuracy by dataset</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{7822728C-3250-4F1A-B04C-F4F4735CF63A}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.16</cx:f>
+              <cx:v>MLP</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{E7D34A0F-AEA9-42D3-9CA0-D09AEAAC7B48}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.18</cx:f>
+              <cx:v>CNN</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="1"/>
+          <cx:layoutPr>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{07A9782B-8CAC-4CAD-9546-92C4F6AAAC4A}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.20</cx:f>
+              <cx:v>RESNET</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="2"/>
+          <cx:layoutPr>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0" hidden="1">
+        <cx:catScaling gapWidth="1.5"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling min="0.10000000000000001"/>
         <cx:majorGridlines/>
         <cx:minorGridlines/>
         <cx:tickLabels/>
@@ -846,8 +3748,183 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="20">
+  <a:schemeClr val="dk1"/>
+  <cs:variation>
+    <a:tint val="88500"/>
+  </cs:variation>
+  <cs:variation>
+    <a:tint val="55000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:tint val="75000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:tint val="98500"/>
+  </cs:variation>
+  <cs:variation>
+    <a:tint val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:tint val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:tint val="80000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="20">
+  <a:schemeClr val="dk1"/>
+  <cs:variation>
+    <a:tint val="88500"/>
+  </cs:variation>
+  <cs:variation>
+    <a:tint val="55000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:tint val="75000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:tint val="98500"/>
+  </cs:variation>
+  <cs:variation>
+    <a:tint val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:tint val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:tint val="80000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="20">
+  <a:schemeClr val="dk1"/>
+  <cs:variation>
+    <a:tint val="88500"/>
+  </cs:variation>
+  <cs:variation>
+    <a:tint val="55000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:tint val="75000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:tint val="98500"/>
+  </cs:variation>
+  <cs:variation>
+    <a:tint val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:tint val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:tint val="80000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="20">
+  <a:schemeClr val="dk1"/>
+  <cs:variation>
+    <a:tint val="88500"/>
+  </cs:variation>
+  <cs:variation>
+    <a:tint val="55000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:tint val="75000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:tint val="98500"/>
+  </cs:variation>
+  <cs:variation>
+    <a:tint val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:tint val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:tint val="80000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="20">
+  <a:schemeClr val="dk1"/>
+  <cs:variation>
+    <a:tint val="88500"/>
+  </cs:variation>
+  <cs:variation>
+    <a:tint val="55000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:tint val="75000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:tint val="98500"/>
+  </cs:variation>
+  <cs:variation>
+    <a:tint val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:tint val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:tint val="80000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="374">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="373">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -858,7 +3935,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" cap="all"/>
+    <cs:defRPr sz="900"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -888,7 +3965,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -904,7 +3981,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900"/>
+    <cs:defRPr sz="1000"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -912,8 +3989,8 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900"/>
@@ -923,18 +4000,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
+      <a:schemeClr val="dk1">
         <a:lumMod val="65000"/>
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
+        <a:schemeClr val="lt1"/>
       </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
@@ -950,6 +4032,516 @@
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="374">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
       <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
@@ -1338,6 +4930,2726 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="dk1"/>
     </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="250">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="15875">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="800" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="major">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="374">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:lumMod val="60000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="8"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="28575">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="major">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="2000"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="28575">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="250">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="15875">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="800" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="major">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="374">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:lumMod val="60000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="8"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="28575">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="major">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="2000"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="28575">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="250">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="15875">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="800" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="major">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -1391,8 +7703,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1506564" y="683009"/>
-              <a:ext cx="4595191" cy="2709198"/>
+              <a:off x="1499938" y="684997"/>
+              <a:ext cx="4572000" cy="2719137"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1425,14 +7737,491 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>686873</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>21465</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>270036</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>176353</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="Chart 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{022DEC56-6D74-423E-8AAD-D1CAC585A703}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7903013" y="1118745"/>
+              <a:ext cx="4581883" cy="2715208"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>697604</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>42930</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>525886</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>21465</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42E2EAAB-8AB2-472D-83FB-2ED918A64DB5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>41189</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>102972</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>378967</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>82158</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="Chart 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57DEF978-945C-4320-8225-127B99F7D9AD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7409729" y="1017372"/>
+              <a:ext cx="4604978" cy="2722386"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>556054</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>61783</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>102973</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D4ED42E-D880-4D5F-A6BB-2B77C3A055EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>8758</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>8759</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>312225</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>142922</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="Chart 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9AD3BC18-B03D-4E86-A561-7E63A8E810A4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7567798" y="923159"/>
+              <a:ext cx="4570667" cy="2694483"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>362263</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>99936</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>87443</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>112426</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FA05A71-D939-471E-A2AC-5E9B63088360}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E212CE2C-A200-49AB-9B6B-A1462F2A19E9}" name="Table2" displayName="Table2" ref="L5:O20" totalsRowShown="0" dataDxfId="3" dataCellStyle="Percent">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E212CE2C-A200-49AB-9B6B-A1462F2A19E9}" name="Table2" displayName="Table2" ref="L5:O20" totalsRowShown="0" dataDxfId="35" dataCellStyle="Percent">
   <autoFilter ref="L5:O20" xr:uid="{E212CE2C-A200-49AB-9B6B-A1462F2A19E9}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{DF8591C0-BA9E-48F6-873B-CBE8216B9F8E}" name="NN"/>
-    <tableColumn id="2" xr3:uid="{17A7B3B9-E69D-4263-89AD-CE3FCF97694A}" name="MLP" dataDxfId="2" dataCellStyle="Percent"/>
-    <tableColumn id="3" xr3:uid="{645DD193-BFB7-4046-AB3A-FE0027D101AB}" name="CNN" dataDxfId="1" dataCellStyle="Percent"/>
-    <tableColumn id="4" xr3:uid="{E3F2AD4B-483D-4819-8B6E-21E26C9EDC0F}" name="RESNET" dataDxfId="0" dataCellStyle="Percent"/>
+    <tableColumn id="2" xr3:uid="{17A7B3B9-E69D-4263-89AD-CE3FCF97694A}" name="MLP" dataDxfId="34" dataCellStyle="Percent"/>
+    <tableColumn id="3" xr3:uid="{645DD193-BFB7-4046-AB3A-FE0027D101AB}" name="CNN" dataDxfId="33" dataCellStyle="Percent"/>
+    <tableColumn id="4" xr3:uid="{E3F2AD4B-483D-4819-8B6E-21E26C9EDC0F}" name="RESNET" dataDxfId="32" dataCellStyle="Percent"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8A3D5F5-2373-4B01-9DCA-87F03530AA6F}" name="Table22" displayName="Table22" ref="L23:O28" totalsRowShown="0" dataDxfId="31" dataCellStyle="Percent">
+  <autoFilter ref="L23:O28" xr:uid="{C8A3D5F5-2373-4B01-9DCA-87F03530AA6F}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{10E6FE1C-D520-4A12-8F7C-555FDB123316}" name="NN"/>
+    <tableColumn id="2" xr3:uid="{06435BC8-288B-4CE9-A54F-5A2047F7278B}" name="MLP" dataDxfId="30" dataCellStyle="Percent"/>
+    <tableColumn id="3" xr3:uid="{239F0B85-BF9B-40F2-97EF-789B861A0A70}" name="CNN" dataDxfId="29" dataCellStyle="Percent"/>
+    <tableColumn id="4" xr3:uid="{578A9646-6545-4EB8-AA44-8F618EF33B96}" name="RESNET" dataDxfId="28" dataCellStyle="Percent"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A8364D7E-3025-4FD7-A14B-AD32C940CE54}" name="Table24" displayName="Table24" ref="L30:O35" totalsRowShown="0" dataDxfId="27" dataCellStyle="Percent">
+  <autoFilter ref="L30:O35" xr:uid="{A8364D7E-3025-4FD7-A14B-AD32C940CE54}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{55BEF93E-02B5-41DD-910A-EB8871CDB1D9}" name="NN"/>
+    <tableColumn id="2" xr3:uid="{8E0B03F1-1D2F-4E09-BB16-42818268A2DD}" name="MLP" dataDxfId="26" dataCellStyle="Percent"/>
+    <tableColumn id="3" xr3:uid="{23403A2F-A507-4A0E-B17B-D913FE6D2DE8}" name="CNN" dataDxfId="25" dataCellStyle="Percent"/>
+    <tableColumn id="4" xr3:uid="{0ECD666C-4AA7-4122-AD56-30E746C29E6D}" name="RESNET" dataDxfId="24" dataCellStyle="Percent"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{158B2213-2D6D-4C06-B4E2-D3801851D188}" name="Table25" displayName="Table25" ref="Q5:T20" totalsRowShown="0" dataDxfId="23" dataCellStyle="Percent">
+  <autoFilter ref="Q5:T20" xr:uid="{158B2213-2D6D-4C06-B4E2-D3801851D188}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{16DC405B-601A-4336-BF0F-BD407A26CF50}" name="NN"/>
+    <tableColumn id="2" xr3:uid="{F13DE317-D420-461E-8750-F55018764EE9}" name="MLP" dataDxfId="22" dataCellStyle="Comma"/>
+    <tableColumn id="3" xr3:uid="{528C723E-99E9-4CCB-B402-8E1A9276BD73}" name="CNN" dataDxfId="21" dataCellStyle="Comma"/>
+    <tableColumn id="4" xr3:uid="{55D41D9A-1C33-4908-A36B-5097EBE45089}" name="RESNET" dataDxfId="20" dataCellStyle="Comma"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{E2AF7887-7922-4F1B-B04D-3A6DE28F8A7C}" name="Table226" displayName="Table226" ref="Q23:T28" totalsRowShown="0" dataDxfId="19" dataCellStyle="Percent">
+  <autoFilter ref="Q23:T28" xr:uid="{E2AF7887-7922-4F1B-B04D-3A6DE28F8A7C}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{EC733CBB-4DCA-4959-9900-9D8F3A03B95C}" name="NN"/>
+    <tableColumn id="2" xr3:uid="{D042DAF6-01DC-4CD0-9AA6-0F6A380E68C4}" name="MLP" dataDxfId="18" dataCellStyle="Comma"/>
+    <tableColumn id="3" xr3:uid="{C5470836-9D09-45E2-9801-85F2CC7ACB75}" name="CNN" dataDxfId="17" dataCellStyle="Comma"/>
+    <tableColumn id="4" xr3:uid="{4FDC3DE6-0D6D-49EC-BF56-F73A38263F98}" name="RESNET" dataDxfId="16" dataCellStyle="Comma"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2DBD2E38-76A4-4B6A-937C-B550CCC9D9DE}" name="Table247" displayName="Table247" ref="Q30:T35" totalsRowShown="0" dataDxfId="15" dataCellStyle="Percent">
+  <autoFilter ref="Q30:T35" xr:uid="{2DBD2E38-76A4-4B6A-937C-B550CCC9D9DE}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{AA762A3F-BFE3-4372-B4F5-FBB998811EF9}" name="NN"/>
+    <tableColumn id="2" xr3:uid="{EC2D1ED0-91B6-4FCB-9575-EA6D9EB88FC5}" name="MLP" dataDxfId="14" dataCellStyle="Comma"/>
+    <tableColumn id="3" xr3:uid="{027B7FD6-0C5E-4A1D-BC89-D09E8166260D}" name="CNN" dataDxfId="13" dataCellStyle="Comma"/>
+    <tableColumn id="4" xr3:uid="{F058F7F6-AAB8-4F96-9759-5BB397137A3A}" name="RESNET" dataDxfId="12" dataCellStyle="Comma"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{2405C85A-0D45-481D-B3BD-AFBBD509AE06}" name="Table28" displayName="Table28" ref="L41:O44" totalsRowShown="0" dataDxfId="11" dataCellStyle="Percent">
+  <autoFilter ref="L41:O44" xr:uid="{2405C85A-0D45-481D-B3BD-AFBBD509AE06}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{26C0E428-9EBD-41D5-8298-8C7655602963}" name="NN"/>
+    <tableColumn id="2" xr3:uid="{99FEBD32-B452-4E81-8C3C-E6C0C3EE682C}" name="MLP" dataDxfId="10" dataCellStyle="Percent">
+      <calculatedColumnFormula>AVERAGE(M6:M10)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{EEE67F0D-4224-4B8C-AB78-2A31AADFA67A}" name="CNN" dataDxfId="9" dataCellStyle="Percent"/>
+    <tableColumn id="4" xr3:uid="{F38F1196-0BC3-4D56-A706-7C8993BA59D7}" name="RESNET" dataDxfId="8" dataCellStyle="Percent"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{4A8A1A7F-1B5A-4867-BB85-ACF1616A330A}" name="Table289" displayName="Table289" ref="Q41:T44" totalsRowShown="0" dataDxfId="7" dataCellStyle="Percent">
+  <autoFilter ref="Q41:T44" xr:uid="{4A8A1A7F-1B5A-4867-BB85-ACF1616A330A}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{807EE56E-ACAD-4B0A-A11F-8BAFB85FB51D}" name="NN"/>
+    <tableColumn id="2" xr3:uid="{799F6690-82C0-4672-8C5A-E57337AB8D14}" name="MLP" dataDxfId="6" dataCellStyle="Comma">
+      <calculatedColumnFormula>AVERAGE(R6:R10)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{A9809BD3-9246-4479-B773-D4AF82AD2BE0}" name="CNN" dataDxfId="5" dataCellStyle="Comma"/>
+    <tableColumn id="4" xr3:uid="{0788FB4A-036B-4B91-B037-915690BA43DC}" name="RESNET" dataDxfId="4" dataCellStyle="Comma"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{2A39B1B6-BE1B-4A46-878D-D41B23190A28}" name="Table2810" displayName="Table2810" ref="O47:R50" totalsRowShown="0" dataDxfId="3" dataCellStyle="Percent">
+  <autoFilter ref="O47:R50" xr:uid="{2A39B1B6-BE1B-4A46-878D-D41B23190A28}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{9B8795FD-B968-49F4-8DD6-44833A152352}" name="NN"/>
+    <tableColumn id="2" xr3:uid="{DE2073A6-8247-482C-BE79-D968BEE14AE7}" name="MLP" dataDxfId="2" dataCellStyle="Percent">
+      <calculatedColumnFormula>R42/(100*M42)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{3CA03A83-37C3-4CFD-9124-5865AE7748FA}" name="CNN" dataDxfId="1" dataCellStyle="Percent">
+      <calculatedColumnFormula>S42/(100*N42)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{2C3D1B9B-2164-40CC-9F5B-081A65625AD4}" name="RESNET" dataDxfId="0" dataCellStyle="Percent">
+      <calculatedColumnFormula>T42/(100*O42)</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1755,14 +8544,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D75B9821-E02D-41EF-A9CC-93791136D914}">
-  <dimension ref="L5:O20"/>
+  <dimension ref="L5:T52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="12" max="12" width="10.44140625" customWidth="1"/>
     <col min="15" max="15" width="9.21875" customWidth="1"/>
+    <col min="16" max="16" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="12:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="12:20" x14ac:dyDescent="0.3">
       <c r="L5" t="s">
         <v>12</v>
       </c>
@@ -1775,8 +8569,20 @@
       <c r="O5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="12:15" x14ac:dyDescent="0.3">
+      <c r="Q5" t="s">
+        <v>12</v>
+      </c>
+      <c r="R5" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="S5" s="60" t="s">
+        <v>6</v>
+      </c>
+      <c r="T5" s="60" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="12:20" x14ac:dyDescent="0.3">
       <c r="L6" t="s">
         <v>14</v>
       </c>
@@ -1789,8 +8595,20 @@
       <c r="O6" s="49">
         <v>0.98485</v>
       </c>
-    </row>
-    <row r="7" spans="12:15" x14ac:dyDescent="0.3">
+      <c r="Q6" t="s">
+        <v>14</v>
+      </c>
+      <c r="R6" s="60">
+        <v>472.3494</v>
+      </c>
+      <c r="S6" s="60">
+        <v>645.86260000000004</v>
+      </c>
+      <c r="T6" s="60">
+        <v>25808.720300000001</v>
+      </c>
+    </row>
+    <row r="7" spans="12:20" x14ac:dyDescent="0.3">
       <c r="L7" t="s">
         <v>14</v>
       </c>
@@ -1803,8 +8621,20 @@
       <c r="O7" s="34">
         <v>0.98023000000000005</v>
       </c>
-    </row>
-    <row r="8" spans="12:15" x14ac:dyDescent="0.3">
+      <c r="Q7" t="s">
+        <v>14</v>
+      </c>
+      <c r="R7" s="60">
+        <v>490.38990000000001</v>
+      </c>
+      <c r="S7" s="60">
+        <v>646.6404</v>
+      </c>
+      <c r="T7" s="60">
+        <v>25925.084699999999</v>
+      </c>
+    </row>
+    <row r="8" spans="12:20" x14ac:dyDescent="0.3">
       <c r="L8" t="s">
         <v>14</v>
       </c>
@@ -1817,8 +8647,20 @@
       <c r="O8" s="34">
         <v>0.98751999999999995</v>
       </c>
-    </row>
-    <row r="9" spans="12:15" x14ac:dyDescent="0.3">
+      <c r="Q8" t="s">
+        <v>14</v>
+      </c>
+      <c r="R8" s="60">
+        <v>496.52519999999998</v>
+      </c>
+      <c r="S8" s="60">
+        <v>652.29919999999993</v>
+      </c>
+      <c r="T8" s="60">
+        <v>26637.750700000001</v>
+      </c>
+    </row>
+    <row r="9" spans="12:20" x14ac:dyDescent="0.3">
       <c r="L9" t="s">
         <v>14</v>
       </c>
@@ -1831,8 +8673,20 @@
       <c r="O9" s="34">
         <v>0.98323000000000005</v>
       </c>
-    </row>
-    <row r="10" spans="12:15" x14ac:dyDescent="0.3">
+      <c r="Q9" t="s">
+        <v>14</v>
+      </c>
+      <c r="R9" s="60">
+        <v>488.34199999999998</v>
+      </c>
+      <c r="S9" s="60">
+        <v>686.78399999999999</v>
+      </c>
+      <c r="T9" s="60">
+        <v>26279.435400000002</v>
+      </c>
+    </row>
+    <row r="10" spans="12:20" x14ac:dyDescent="0.3">
       <c r="L10" t="s">
         <v>14</v>
       </c>
@@ -1845,8 +8699,20 @@
       <c r="O10" s="50">
         <v>0.98951999999999996</v>
       </c>
-    </row>
-    <row r="11" spans="12:15" x14ac:dyDescent="0.3">
+      <c r="Q10" t="s">
+        <v>14</v>
+      </c>
+      <c r="R10" s="60">
+        <v>506.02140000000003</v>
+      </c>
+      <c r="S10" s="60">
+        <v>662.71040000000005</v>
+      </c>
+      <c r="T10" s="60">
+        <v>25764.280300000002</v>
+      </c>
+    </row>
+    <row r="11" spans="12:20" x14ac:dyDescent="0.3">
       <c r="L11" t="s">
         <v>15</v>
       </c>
@@ -1859,8 +8725,20 @@
       <c r="O11" s="49">
         <v>0.69606000000000001</v>
       </c>
-    </row>
-    <row r="12" spans="12:15" x14ac:dyDescent="0.3">
+      <c r="Q11" t="s">
+        <v>15</v>
+      </c>
+      <c r="R11" s="60">
+        <v>2597.5892000000003</v>
+      </c>
+      <c r="S11" s="60">
+        <v>3340.0242000000003</v>
+      </c>
+      <c r="T11" s="61">
+        <v>131587.87600000002</v>
+      </c>
+    </row>
+    <row r="12" spans="12:20" x14ac:dyDescent="0.3">
       <c r="L12" t="s">
         <v>15</v>
       </c>
@@ -1873,8 +8751,20 @@
       <c r="O12" s="34">
         <v>0.70364000000000004</v>
       </c>
-    </row>
-    <row r="13" spans="12:15" x14ac:dyDescent="0.3">
+      <c r="Q12" t="s">
+        <v>15</v>
+      </c>
+      <c r="R12" s="60">
+        <v>2615.6130000000003</v>
+      </c>
+      <c r="S12" s="60">
+        <v>3268.837</v>
+      </c>
+      <c r="T12" s="62">
+        <v>130909.30599999998</v>
+      </c>
+    </row>
+    <row r="13" spans="12:20" x14ac:dyDescent="0.3">
       <c r="L13" t="s">
         <v>15</v>
       </c>
@@ -1887,8 +8777,20 @@
       <c r="O13" s="34">
         <v>0.71728000000000003</v>
       </c>
-    </row>
-    <row r="14" spans="12:15" x14ac:dyDescent="0.3">
+      <c r="Q13" t="s">
+        <v>15</v>
+      </c>
+      <c r="R13" s="60">
+        <v>2629.99</v>
+      </c>
+      <c r="S13" s="60">
+        <v>3344.7112000000002</v>
+      </c>
+      <c r="T13" s="62">
+        <v>129065.30399999999</v>
+      </c>
+    </row>
+    <row r="14" spans="12:20" x14ac:dyDescent="0.3">
       <c r="L14" t="s">
         <v>15</v>
       </c>
@@ -1901,8 +8803,20 @@
       <c r="O14" s="34">
         <v>0.71479999999999999</v>
       </c>
-    </row>
-    <row r="15" spans="12:15" x14ac:dyDescent="0.3">
+      <c r="Q14" t="s">
+        <v>15</v>
+      </c>
+      <c r="R14" s="60">
+        <v>2695.7507999999998</v>
+      </c>
+      <c r="S14" s="60">
+        <v>3249.5574999999999</v>
+      </c>
+      <c r="T14" s="62">
+        <v>125967.626</v>
+      </c>
+    </row>
+    <row r="15" spans="12:20" x14ac:dyDescent="0.3">
       <c r="L15" t="s">
         <v>15</v>
       </c>
@@ -1915,8 +8829,20 @@
       <c r="O15" s="50">
         <v>0.73358000000000001</v>
       </c>
-    </row>
-    <row r="16" spans="12:15" x14ac:dyDescent="0.3">
+      <c r="Q15" t="s">
+        <v>15</v>
+      </c>
+      <c r="R15" s="60">
+        <v>2646.8458000000001</v>
+      </c>
+      <c r="S15" s="60">
+        <v>3216.8111999999996</v>
+      </c>
+      <c r="T15" s="63">
+        <v>125672.97600000001</v>
+      </c>
+    </row>
+    <row r="16" spans="12:20" x14ac:dyDescent="0.3">
       <c r="L16" t="s">
         <v>16</v>
       </c>
@@ -1929,8 +8855,20 @@
       <c r="O16" s="33">
         <v>0.31286000000000003</v>
       </c>
-    </row>
-    <row r="17" spans="12:15" x14ac:dyDescent="0.3">
+      <c r="Q16" t="s">
+        <v>16</v>
+      </c>
+      <c r="R16" s="60">
+        <v>6637.5852999999997</v>
+      </c>
+      <c r="S16" s="60">
+        <v>7972.7319000000007</v>
+      </c>
+      <c r="T16" s="60">
+        <v>333859.96299999999</v>
+      </c>
+    </row>
+    <row r="17" spans="12:20" x14ac:dyDescent="0.3">
       <c r="L17" t="s">
         <v>16</v>
       </c>
@@ -1943,8 +8881,20 @@
       <c r="O17" s="33">
         <v>0.32181999999999999</v>
       </c>
-    </row>
-    <row r="18" spans="12:15" x14ac:dyDescent="0.3">
+      <c r="Q17" t="s">
+        <v>16</v>
+      </c>
+      <c r="R17" s="60">
+        <v>6661.7039999999997</v>
+      </c>
+      <c r="S17" s="60">
+        <v>8151.5667999999996</v>
+      </c>
+      <c r="T17" s="60">
+        <v>326162.473</v>
+      </c>
+    </row>
+    <row r="18" spans="12:20" x14ac:dyDescent="0.3">
       <c r="L18" t="s">
         <v>16</v>
       </c>
@@ -1957,8 +8907,20 @@
       <c r="O18" s="33">
         <v>0.3165</v>
       </c>
-    </row>
-    <row r="19" spans="12:15" x14ac:dyDescent="0.3">
+      <c r="Q18" t="s">
+        <v>16</v>
+      </c>
+      <c r="R18" s="60">
+        <v>6283.0973999999997</v>
+      </c>
+      <c r="S18" s="60">
+        <v>8386.5390000000007</v>
+      </c>
+      <c r="T18" s="60">
+        <v>340349.97599999997</v>
+      </c>
+    </row>
+    <row r="19" spans="12:20" x14ac:dyDescent="0.3">
       <c r="L19" t="s">
         <v>16</v>
       </c>
@@ -1971,8 +8933,20 @@
       <c r="O19" s="33">
         <v>0.33235999999999999</v>
       </c>
-    </row>
-    <row r="20" spans="12:15" x14ac:dyDescent="0.3">
+      <c r="Q19" t="s">
+        <v>16</v>
+      </c>
+      <c r="R19" s="60">
+        <v>6629.2352999999994</v>
+      </c>
+      <c r="S19" s="60">
+        <v>8281.4526000000005</v>
+      </c>
+      <c r="T19" s="60">
+        <v>318932.64</v>
+      </c>
+    </row>
+    <row r="20" spans="12:20" x14ac:dyDescent="0.3">
       <c r="L20" t="s">
         <v>16</v>
       </c>
@@ -1984,14 +8958,547 @@
       </c>
       <c r="O20" s="33">
         <v>0.31991999999999998</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>16</v>
+      </c>
+      <c r="R20" s="60">
+        <v>6485.6275000000005</v>
+      </c>
+      <c r="S20" s="60">
+        <v>8448.9944000000014</v>
+      </c>
+      <c r="T20" s="60">
+        <v>310033.141</v>
+      </c>
+    </row>
+    <row r="23" spans="12:20" x14ac:dyDescent="0.3">
+      <c r="L23" t="s">
+        <v>12</v>
+      </c>
+      <c r="M23" t="s">
+        <v>9</v>
+      </c>
+      <c r="N23" t="s">
+        <v>6</v>
+      </c>
+      <c r="O23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>12</v>
+      </c>
+      <c r="R23" t="s">
+        <v>9</v>
+      </c>
+      <c r="S23" t="s">
+        <v>6</v>
+      </c>
+      <c r="T23" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="12:20" x14ac:dyDescent="0.3">
+      <c r="L24" t="s">
+        <v>15</v>
+      </c>
+      <c r="M24" s="33">
+        <v>0.42558000000000001</v>
+      </c>
+      <c r="N24" s="33">
+        <v>0.59211999999999998</v>
+      </c>
+      <c r="O24" s="49">
+        <v>0.69606000000000001</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>15</v>
+      </c>
+      <c r="R24" s="60">
+        <v>2597.5892000000003</v>
+      </c>
+      <c r="S24" s="60">
+        <v>3340.0242000000003</v>
+      </c>
+      <c r="T24" s="61">
+        <v>131587.87600000002</v>
+      </c>
+    </row>
+    <row r="25" spans="12:20" x14ac:dyDescent="0.3">
+      <c r="L25" t="s">
+        <v>15</v>
+      </c>
+      <c r="M25" s="33">
+        <v>0.4219</v>
+      </c>
+      <c r="N25" s="33">
+        <v>0.59199999999999997</v>
+      </c>
+      <c r="O25" s="34">
+        <v>0.70364000000000004</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>15</v>
+      </c>
+      <c r="R25" s="60">
+        <v>2615.6130000000003</v>
+      </c>
+      <c r="S25" s="60">
+        <v>3268.837</v>
+      </c>
+      <c r="T25" s="62">
+        <v>130909.30599999998</v>
+      </c>
+    </row>
+    <row r="26" spans="12:20" x14ac:dyDescent="0.3">
+      <c r="L26" t="s">
+        <v>15</v>
+      </c>
+      <c r="M26" s="33">
+        <v>0.42796000000000001</v>
+      </c>
+      <c r="N26" s="33">
+        <v>0.59275999999999995</v>
+      </c>
+      <c r="O26" s="34">
+        <v>0.71728000000000003</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>15</v>
+      </c>
+      <c r="R26" s="60">
+        <v>2629.99</v>
+      </c>
+      <c r="S26" s="60">
+        <v>3344.7112000000002</v>
+      </c>
+      <c r="T26" s="62">
+        <v>129065.30399999999</v>
+      </c>
+    </row>
+    <row r="27" spans="12:20" x14ac:dyDescent="0.3">
+      <c r="L27" t="s">
+        <v>15</v>
+      </c>
+      <c r="M27" s="33">
+        <v>0.43668000000000001</v>
+      </c>
+      <c r="N27" s="33">
+        <v>0.59489999999999998</v>
+      </c>
+      <c r="O27" s="34">
+        <v>0.71479999999999999</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>15</v>
+      </c>
+      <c r="R27" s="60">
+        <v>2695.7507999999998</v>
+      </c>
+      <c r="S27" s="60">
+        <v>3249.5574999999999</v>
+      </c>
+      <c r="T27" s="62">
+        <v>125967.626</v>
+      </c>
+    </row>
+    <row r="28" spans="12:20" x14ac:dyDescent="0.3">
+      <c r="L28" t="s">
+        <v>15</v>
+      </c>
+      <c r="M28" s="33">
+        <v>0.42558000000000001</v>
+      </c>
+      <c r="N28" s="33">
+        <v>0.57767999999999997</v>
+      </c>
+      <c r="O28" s="50">
+        <v>0.73358000000000001</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>15</v>
+      </c>
+      <c r="R28" s="60">
+        <v>2646.8458000000001</v>
+      </c>
+      <c r="S28" s="60">
+        <v>3216.8111999999996</v>
+      </c>
+      <c r="T28" s="63">
+        <v>125672.97600000001</v>
+      </c>
+    </row>
+    <row r="30" spans="12:20" x14ac:dyDescent="0.3">
+      <c r="L30" t="s">
+        <v>12</v>
+      </c>
+      <c r="M30" t="s">
+        <v>9</v>
+      </c>
+      <c r="N30" t="s">
+        <v>6</v>
+      </c>
+      <c r="O30" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>12</v>
+      </c>
+      <c r="R30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S30" t="s">
+        <v>6</v>
+      </c>
+      <c r="T30" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="12:20" x14ac:dyDescent="0.3">
+      <c r="L31" t="s">
+        <v>16</v>
+      </c>
+      <c r="M31" s="33">
+        <v>0.14152000000000001</v>
+      </c>
+      <c r="N31" s="33">
+        <v>0.21504000000000001</v>
+      </c>
+      <c r="O31" s="33">
+        <v>0.31286000000000003</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>16</v>
+      </c>
+      <c r="R31" s="60">
+        <v>6637.5852999999997</v>
+      </c>
+      <c r="S31" s="60">
+        <v>7972.7319000000007</v>
+      </c>
+      <c r="T31" s="60">
+        <v>333859.96299999999</v>
+      </c>
+    </row>
+    <row r="32" spans="12:20" x14ac:dyDescent="0.3">
+      <c r="L32" t="s">
+        <v>16</v>
+      </c>
+      <c r="M32" s="33">
+        <v>0.14566000000000001</v>
+      </c>
+      <c r="N32" s="33">
+        <v>0.20785999999999999</v>
+      </c>
+      <c r="O32" s="33">
+        <v>0.32181999999999999</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>16</v>
+      </c>
+      <c r="R32" s="60">
+        <v>6661.7039999999997</v>
+      </c>
+      <c r="S32" s="60">
+        <v>8151.5667999999996</v>
+      </c>
+      <c r="T32" s="60">
+        <v>326162.473</v>
+      </c>
+    </row>
+    <row r="33" spans="12:20" x14ac:dyDescent="0.3">
+      <c r="L33" t="s">
+        <v>16</v>
+      </c>
+      <c r="M33" s="33">
+        <v>0.1484</v>
+      </c>
+      <c r="N33" s="33">
+        <v>0.20391999999999999</v>
+      </c>
+      <c r="O33" s="33">
+        <v>0.3165</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>16</v>
+      </c>
+      <c r="R33" s="60">
+        <v>6283.0973999999997</v>
+      </c>
+      <c r="S33" s="60">
+        <v>8386.5390000000007</v>
+      </c>
+      <c r="T33" s="60">
+        <v>340349.97599999997</v>
+      </c>
+    </row>
+    <row r="34" spans="12:20" x14ac:dyDescent="0.3">
+      <c r="L34" t="s">
+        <v>16</v>
+      </c>
+      <c r="M34" s="33">
+        <v>0.15104000000000001</v>
+      </c>
+      <c r="N34" s="33">
+        <v>0.2059</v>
+      </c>
+      <c r="O34" s="33">
+        <v>0.33235999999999999</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>16</v>
+      </c>
+      <c r="R34" s="60">
+        <v>6629.2352999999994</v>
+      </c>
+      <c r="S34" s="60">
+        <v>8281.4526000000005</v>
+      </c>
+      <c r="T34" s="60">
+        <v>318932.64</v>
+      </c>
+    </row>
+    <row r="35" spans="12:20" x14ac:dyDescent="0.3">
+      <c r="L35" t="s">
+        <v>16</v>
+      </c>
+      <c r="M35" s="33">
+        <v>0.15068000000000001</v>
+      </c>
+      <c r="N35" s="33">
+        <v>0.20172000000000001</v>
+      </c>
+      <c r="O35" s="33">
+        <v>0.31991999999999998</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>16</v>
+      </c>
+      <c r="R35" s="60">
+        <v>6485.6275000000005</v>
+      </c>
+      <c r="S35" s="60">
+        <v>8448.9944000000014</v>
+      </c>
+      <c r="T35" s="60">
+        <v>310033.141</v>
+      </c>
+    </row>
+    <row r="41" spans="12:20" x14ac:dyDescent="0.3">
+      <c r="L41" t="s">
+        <v>12</v>
+      </c>
+      <c r="M41" t="s">
+        <v>9</v>
+      </c>
+      <c r="N41" t="s">
+        <v>6</v>
+      </c>
+      <c r="O41" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>12</v>
+      </c>
+      <c r="R41" t="s">
+        <v>9</v>
+      </c>
+      <c r="S41" t="s">
+        <v>6</v>
+      </c>
+      <c r="T41" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="12:20" x14ac:dyDescent="0.3">
+      <c r="L42" t="s">
+        <v>14</v>
+      </c>
+      <c r="M42" s="2">
+        <f>AVERAGE(M6:M10)</f>
+        <v>0.95430000000000015</v>
+      </c>
+      <c r="N42" s="2">
+        <f>AVERAGE(N6:N10)</f>
+        <v>0.98008348000000001</v>
+      </c>
+      <c r="O42" s="2">
+        <f>AVERAGE(O6:O10)</f>
+        <v>0.98507</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>14</v>
+      </c>
+      <c r="R42" s="60">
+        <f>AVERAGE(R6:R10)</f>
+        <v>490.72557999999998</v>
+      </c>
+      <c r="S42" s="60">
+        <f>AVERAGE(S6:S10)</f>
+        <v>658.85932000000003</v>
+      </c>
+      <c r="T42" s="60">
+        <f>AVERAGE(T6:T10)</f>
+        <v>26083.05428</v>
+      </c>
+    </row>
+    <row r="43" spans="12:20" x14ac:dyDescent="0.3">
+      <c r="L43" t="s">
+        <v>15</v>
+      </c>
+      <c r="M43" s="2">
+        <f>AVERAGE(M11:M15)</f>
+        <v>0.42754000000000003</v>
+      </c>
+      <c r="N43" s="2">
+        <f>AVERAGE(N11:N15)</f>
+        <v>0.58989200000000008</v>
+      </c>
+      <c r="O43" s="2">
+        <f>AVERAGE(O11:O15)</f>
+        <v>0.71307200000000004</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>15</v>
+      </c>
+      <c r="R43" s="60">
+        <f>AVERAGE(R11:R15)</f>
+        <v>2637.1577599999996</v>
+      </c>
+      <c r="S43" s="60">
+        <f>AVERAGE(S11:S15)</f>
+        <v>3283.9882200000002</v>
+      </c>
+      <c r="T43" s="60">
+        <f>AVERAGE(T11:T15)</f>
+        <v>128640.6176</v>
+      </c>
+    </row>
+    <row r="44" spans="12:20" x14ac:dyDescent="0.3">
+      <c r="L44" t="s">
+        <v>16</v>
+      </c>
+      <c r="M44" s="2">
+        <f>AVERAGE(M16:M20)</f>
+        <v>0.14745999999999998</v>
+      </c>
+      <c r="N44" s="2">
+        <f>AVERAGE(N16:N20)</f>
+        <v>0.20688800000000002</v>
+      </c>
+      <c r="O44" s="2">
+        <f>AVERAGE(O16:O20)</f>
+        <v>0.32069199999999998</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>16</v>
+      </c>
+      <c r="R44" s="60">
+        <f>AVERAGE(R16:R20)</f>
+        <v>6539.4498999999996</v>
+      </c>
+      <c r="S44" s="60">
+        <f>AVERAGE(S16:S20)</f>
+        <v>8248.2569400000011</v>
+      </c>
+      <c r="T44" s="60">
+        <f>AVERAGE(T16:T20)</f>
+        <v>325867.63860000006</v>
+      </c>
+    </row>
+    <row r="47" spans="12:20" x14ac:dyDescent="0.3">
+      <c r="O47" t="s">
+        <v>12</v>
+      </c>
+      <c r="P47" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>6</v>
+      </c>
+      <c r="R47" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="12:20" x14ac:dyDescent="0.3">
+      <c r="O48" t="s">
+        <v>14</v>
+      </c>
+      <c r="P48" s="59">
+        <f>R42/(100*M42)</f>
+        <v>5.1422569422613424</v>
+      </c>
+      <c r="Q48" s="59">
+        <f t="shared" ref="Q48:R50" si="0">S42/(100*N42)</f>
+        <v>6.7224816400333571</v>
+      </c>
+      <c r="R48" s="59">
+        <f t="shared" si="0"/>
+        <v>264.78376440252975</v>
+      </c>
+    </row>
+    <row r="49" spans="15:18" x14ac:dyDescent="0.3">
+      <c r="O49" t="s">
+        <v>15</v>
+      </c>
+      <c r="P49" s="59">
+        <f t="shared" ref="P49:P50" si="1">R43/(100*M43)</f>
+        <v>61.682129391401958</v>
+      </c>
+      <c r="Q49" s="59">
+        <f t="shared" si="0"/>
+        <v>55.671007913312941</v>
+      </c>
+      <c r="R49" s="59">
+        <f t="shared" si="0"/>
+        <v>1804.0340610765811</v>
+      </c>
+    </row>
+    <row r="50" spans="15:18" x14ac:dyDescent="0.3">
+      <c r="O50" t="s">
+        <v>16</v>
+      </c>
+      <c r="P50" s="59">
+        <f t="shared" si="1"/>
+        <v>443.47279940322801</v>
+      </c>
+      <c r="Q50" s="59">
+        <f t="shared" si="0"/>
+        <v>398.68223096554664</v>
+      </c>
+      <c r="R50" s="59">
+        <f t="shared" si="0"/>
+        <v>10161.389701021544</v>
+      </c>
+    </row>
+    <row r="52" spans="15:18" x14ac:dyDescent="0.3">
+      <c r="P52">
+        <f>AVERAGE(Table2810[MLP])</f>
+        <v>170.09906191229712</v>
+      </c>
+      <c r="Q52">
+        <f>AVERAGE(Table2810[CNN])</f>
+        <v>153.69190683963097</v>
+      </c>
+      <c r="R52">
+        <f>AVERAGE(Table2810[RESNET])</f>
+        <v>4076.735842166885</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
-  <tableParts count="1">
+  <tableParts count="9">
     <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
+    <tablePart r:id="rId7"/>
+    <tablePart r:id="rId8"/>
+    <tablePart r:id="rId9"/>
+    <tablePart r:id="rId10"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2306,7 +9813,7 @@
         <f t="shared" si="4"/>
         <v>490.72557999999998</v>
       </c>
-      <c r="F19" s="52">
+      <c r="F19" s="51">
         <f t="shared" si="4"/>
         <v>0.95430000000000015</v>
       </c>
@@ -2315,19 +9822,19 @@
       <c r="B20" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="55">
+      <c r="C20" s="54">
         <f>_xlfn.STDEV.S(C14:C18)</f>
         <v>0.77811072476865384</v>
       </c>
-      <c r="D20" s="55">
+      <c r="D20" s="54">
         <f t="shared" ref="D20:F20" si="5">_xlfn.STDEV.S(D14:D18)</f>
         <v>0.48270073544588643</v>
       </c>
-      <c r="E20" s="55">
+      <c r="E20" s="54">
         <f t="shared" si="5"/>
         <v>12.359973985490429</v>
       </c>
-      <c r="F20" s="56">
+      <c r="F20" s="55">
         <f t="shared" si="5"/>
         <v>4.9637032546275359E-3</v>
       </c>
@@ -2336,7 +9843,7 @@
       <c r="A21" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="B21" s="54">
+      <c r="B21" s="53">
         <v>1</v>
       </c>
       <c r="C21" s="44">
@@ -2357,16 +9864,16 @@
       <c r="A22" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="54">
+      <c r="B22" s="53">
         <v>2</v>
       </c>
       <c r="C22" s="46">
         <v>409.55900000000003</v>
       </c>
-      <c r="D22" s="57">
+      <c r="D22">
         <v>63.3</v>
       </c>
-      <c r="E22" s="57">
+      <c r="E22">
         <f t="shared" ref="E22:E25" si="6">C22*D22</f>
         <v>25925.084699999999</v>
       </c>
@@ -2378,16 +9885,16 @@
       <c r="A23" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="B23" s="54">
+      <c r="B23" s="53">
         <v>3</v>
       </c>
       <c r="C23" s="46">
         <v>410.44299999999998</v>
       </c>
-      <c r="D23" s="57">
+      <c r="D23">
         <v>64.900000000000006</v>
       </c>
-      <c r="E23" s="57">
+      <c r="E23">
         <f t="shared" si="6"/>
         <v>26637.750700000001</v>
       </c>
@@ -2399,16 +9906,16 @@
       <c r="A24" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="B24" s="54">
+      <c r="B24" s="53">
         <v>4</v>
       </c>
       <c r="C24" s="46">
         <v>409.33699999999999</v>
       </c>
-      <c r="D24" s="57">
+      <c r="D24">
         <v>64.2</v>
       </c>
-      <c r="E24" s="57">
+      <c r="E24">
         <f t="shared" si="6"/>
         <v>26279.435400000002</v>
       </c>
@@ -2420,7 +9927,7 @@
       <c r="A25" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="B25" s="54">
+      <c r="B25" s="53">
         <v>5</v>
       </c>
       <c r="C25" s="47">
@@ -2441,19 +9948,19 @@
       <c r="B26" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="55">
+      <c r="C26" s="54">
         <f>AVERAGE(C21:C25)</f>
         <v>409.59179999999998</v>
       </c>
-      <c r="D26" s="55">
+      <c r="D26" s="54">
         <f t="shared" ref="D26:F26" si="7">AVERAGE(D21:D25)</f>
         <v>63.679999999999993</v>
       </c>
-      <c r="E26" s="55">
+      <c r="E26" s="54">
         <f t="shared" si="7"/>
         <v>26083.05428</v>
       </c>
-      <c r="F26" s="56">
+      <c r="F26" s="55">
         <f t="shared" si="7"/>
         <v>0.98507</v>
       </c>
@@ -2474,7 +9981,7 @@
         <f t="shared" si="8"/>
         <v>370.16348880134291</v>
       </c>
-      <c r="F27" s="53">
+      <c r="F27" s="52">
         <f t="shared" si="8"/>
         <v>3.6285189816231758E-3</v>
       </c>
@@ -2492,18 +9999,23 @@
       <c r="A31" s="1"/>
     </row>
     <row r="32" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="51" t="s">
+      <c r="A32" s="64" t="s">
         <v>11</v>
       </c>
+      <c r="C32">
+        <f>SUM(C7:C11,C14:C18,C21:C25)</f>
+        <v>2277.585</v>
+      </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="51"/>
+      <c r="A33" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A32:A33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2987,12 +10499,16 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="51" t="s">
+      <c r="A32" s="64" t="s">
         <v>11</v>
       </c>
+      <c r="C32">
+        <f>SUM(C7:C11,C14:C18,C21:C25)</f>
+        <v>11301.635</v>
+      </c>
     </row>
     <row r="33" spans="1:1" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="51"/>
+      <c r="A33" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3000,6 +10516,7 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3054,7 +10571,7 @@
       <c r="D7">
         <v>27.9</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="56">
         <f>C7*D7</f>
         <v>7972.7319000000007</v>
       </c>
@@ -3075,7 +10592,7 @@
       <c r="D8">
         <v>28.4</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="56">
         <f t="shared" ref="E8:E11" si="0">C8*D8</f>
         <v>8151.5667999999996</v>
       </c>
@@ -3096,7 +10613,7 @@
       <c r="D9">
         <v>29.3</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="56">
         <f t="shared" si="0"/>
         <v>8386.5390000000007</v>
       </c>
@@ -3117,7 +10634,7 @@
       <c r="D10">
         <v>29.1</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="56">
         <f t="shared" si="0"/>
         <v>8281.4526000000005</v>
       </c>
@@ -3138,7 +10655,7 @@
       <c r="D11">
         <v>29.6</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="56">
         <f t="shared" si="0"/>
         <v>8448.9944000000014</v>
       </c>
@@ -3158,7 +10675,7 @@
         <f t="shared" ref="D12:F12" si="1">AVERAGE(D7:D11)</f>
         <v>28.859999999999996</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="57">
         <f t="shared" si="1"/>
         <v>8248.2569400000011</v>
       </c>
@@ -3179,7 +10696,7 @@
         <f t="shared" ref="D13:F13" si="2">_xlfn.STDEV.S(D7:D11)</f>
         <v>0.69498201415576355</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="58">
         <f t="shared" si="2"/>
         <v>190.90733265654865</v>
       </c>
@@ -3201,7 +10718,7 @@
       <c r="D14">
         <v>28.1</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="56">
         <f>C14*D14</f>
         <v>6637.5852999999997</v>
       </c>
@@ -3222,7 +10739,7 @@
       <c r="D15">
         <v>28</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="56">
         <f t="shared" ref="E15:E18" si="3">C15*D15</f>
         <v>6661.7039999999997</v>
       </c>
@@ -3243,7 +10760,7 @@
       <c r="D16">
         <v>26.7</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="56">
         <f t="shared" si="3"/>
         <v>6283.0973999999997</v>
       </c>
@@ -3264,7 +10781,7 @@
       <c r="D17">
         <v>27.9</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="56">
         <f t="shared" si="3"/>
         <v>6629.2352999999994</v>
       </c>
@@ -3285,7 +10802,7 @@
       <c r="D18">
         <v>27.5</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="56">
         <f t="shared" si="3"/>
         <v>6485.6275000000005</v>
       </c>
@@ -3305,7 +10822,7 @@
         <f t="shared" ref="D19:F19" si="4">AVERAGE(D14:D18)</f>
         <v>27.639999999999997</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="57">
         <f t="shared" si="4"/>
         <v>6539.4498999999996</v>
       </c>
@@ -3326,7 +10843,7 @@
         <f t="shared" ref="D20:F20" si="5">_xlfn.STDEV.S(D14:D18)</f>
         <v>0.57271284253105448</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="58">
         <f t="shared" si="5"/>
         <v>159.10020015004687</v>
       </c>
@@ -3348,7 +10865,7 @@
       <c r="D21">
         <v>65.3</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="56">
         <f>C21*D21</f>
         <v>333859.96299999999</v>
       </c>
@@ -3369,7 +10886,7 @@
       <c r="D22">
         <v>63.7</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="56">
         <f t="shared" ref="E22:E25" si="6">C22*D22</f>
         <v>326162.473</v>
       </c>
@@ -3390,7 +10907,7 @@
       <c r="D23">
         <v>66.599999999999994</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="56">
         <f t="shared" si="6"/>
         <v>340349.97599999997</v>
       </c>
@@ -3411,7 +10928,7 @@
       <c r="D24">
         <v>62.4</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="56">
         <f t="shared" si="6"/>
         <v>318932.64</v>
       </c>
@@ -3432,7 +10949,7 @@
       <c r="D25">
         <v>60.7</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="56">
         <f t="shared" si="6"/>
         <v>310033.141</v>
       </c>
@@ -3452,7 +10969,7 @@
         <f>AVERAGE(D21:D25)</f>
         <v>63.739999999999995</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E26" s="57">
         <f t="shared" ref="E26:F26" si="7">AVERAGE(E21:E25)</f>
         <v>325867.63860000006</v>
       </c>
@@ -3473,7 +10990,7 @@
         <f>_xlfn.STDEV.S(D21:D25)</f>
         <v>2.3265854809140336</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E27" s="58">
         <f t="shared" ref="E27:F27" si="8">_xlfn.STDEV.S(E21:E25)</f>
         <v>11963.776504851048</v>
       </c>
@@ -3483,18 +11000,23 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="51" t="s">
+      <c r="A32" s="64" t="s">
         <v>11</v>
       </c>
+      <c r="C32">
+        <f>SUM(C7:C11,C14:C18,C21:C25)</f>
+        <v>28174.034000000003</v>
+      </c>
     </row>
     <row r="33" spans="1:1" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="51"/>
+      <c r="A33" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A32:A33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
